--- a/climate_trace_tools/compare/aggregate_up/files/aggregate-up-csv-crosswalks.xlsx
+++ b/climate_trace_tools/compare/aggregate_up/files/aggregate-up-csv-crosswalks.xlsx
@@ -638,11 +638,12 @@
     <col customWidth="1" min="2" max="2" width="39.25"/>
     <col customWidth="1" min="3" max="3" width="33.5"/>
     <col customWidth="1" min="4" max="4" width="40.88"/>
+    <col customWidth="1" min="5" max="5" width="23.38"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""unfccc-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""unfccc-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -6066,7 +6067,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""edgar-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""edgar-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -6122,8 +6123,8 @@
         <v>Fossil Fuel Operations</v>
       </c>
       <c r="C3" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"coal-mining, solid-fuel-transformation, oil-and-gas-production-and-transport, oil-and-gas-refining, other-fossil-fuel-operations")</f>
-        <v>coal-mining, solid-fuel-transformation, oil-and-gas-production-and-transport, oil-and-gas-refining, other-fossil-fuel-operations</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"coal-mining, solid-fuel-transformation, oil-and-gas-production, oil-and-gas-transport, oil-and-gas-refining, other-fossil-fuel-operations")</f>
+        <v>coal-mining, solid-fuel-transformation, oil-and-gas-production, oil-and-gas-transport, oil-and-gas-refining, other-fossil-fuel-operations</v>
       </c>
       <c r="D3" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1.B.1 Solid Fuels, 1.B.2 Oil and Natural Gas, 1.A.1.bc Petroleum Refining - Manufacture of Solid Fuels and Other Energy Industries")</f>
@@ -6266,8 +6267,8 @@
         <v>Residential and Commercial Onsite Fuel Usage</v>
       </c>
       <c r="C9" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"residential-and-commercial-onsite-fuel-usage")</f>
-        <v>residential-and-commercial-onsite-fuel-usage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"residential-onsite-fuel-usage, non-residential-onsite-fuel-usage")</f>
+        <v>residential-onsite-fuel-usage, non-residential-onsite-fuel-usage</v>
       </c>
       <c r="D9" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1.A.4 Residential and other sectors")</f>
@@ -6458,8 +6459,8 @@
         <v>Manure Management</v>
       </c>
       <c r="C17" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"manure-left-on-pasture-cattle, manure-management-cattle-feedlot, manure-management-other")</f>
-        <v>manure-left-on-pasture-cattle, manure-management-cattle-feedlot, manure-management-other</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"manure-management-cattle-feedlot, manure-management-other, manure-left-on-pasture-cattle (CH4)")</f>
+        <v>manure-management-cattle-feedlot, manure-management-other, manure-left-on-pasture-cattle (CH4)</v>
       </c>
       <c r="D17" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"3.A.2 Manure Management")</f>
@@ -6502,12 +6503,14 @@
         <v>Agriculture</v>
       </c>
       <c r="B19" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Synthetic Fertilizer Application")</f>
-        <v>Synthetic Fertilizer Application</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Direct Nitrogen Emissions from Agricultural Soils ")</f>
+        <v>Direct Nitrogen Emissions from Agricultural Soils </v>
       </c>
       <c r="C19" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"synthetic-fertilizer-application")</f>
-        <v>synthetic-fertilizer-application</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"synthetic-fertilizer-application, manure-applied-to-soils, crop-residues
+soil-organic-carbon, manure-left-on-pasture-cattle (N2O)")</f>
+        <v>synthetic-fertilizer-application, manure-applied-to-soils, crop-residues
+soil-organic-carbon, manure-left-on-pasture-cattle (N2O)</v>
       </c>
       <c r="D19" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"3.C.4 Direct N2O Emissions from managed soils")</f>
@@ -6530,8 +6533,8 @@
         <v>Other Agriculture</v>
       </c>
       <c r="C20" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"other-agriculture, other-agricultural-soils")</f>
-        <v>other-agriculture, other-agricultural-soils</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"other-agricultural-soils")</f>
+        <v>other-agricultural-soils</v>
       </c>
       <c r="D20" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"3.C.2 Liming, 3.C.3 Urea application, 3.C.5 Indirect N2O Emissions from managed soils, 3.C.6 Indirect N2O Emissions from manure management, 5.A Indirect N2O emissions from the atmospheric deposition of nitrogen in NOx and NH3")</f>
@@ -6650,8 +6653,8 @@
         <v>Wastewater Treatment and Discharge</v>
       </c>
       <c r="C25" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"wastewater-treatment-and-discharge")</f>
-        <v>wastewater-treatment-and-discharge</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"industrial-wastewater-treatment-and-discharge, domestic-wastewater-treatment-and-discharge")</f>
+        <v>industrial-wastewater-treatment-and-discharge, domestic-wastewater-treatment-and-discharge</v>
       </c>
       <c r="D25" s="9" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"4.D Wastewater Treatment and Discharge")</f>
@@ -8778,7 +8781,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""cait-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""cait-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -11332,7 +11335,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""pik-tp-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""pik-tp-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -13879,7 +13882,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""faostat-analysis-utility!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""faostat-analysis-utility!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -16411,7 +16414,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""carbon-monitor-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""carbon-monitor-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
@@ -18907,7 +18910,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1crBeTIm7isN5EkvLbmkhoZYJqep1xzNwDVNnIu94l6E/edit#gid=0"", ""gcp-analysis-util!A1:J200"")"),"Comparison Sector")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1wLnB8hxKU-7PlYgtI8izkxNTGaHjQtEa8aS_amsvYvI/edit?gid=1161993050#gid=1161993050"", ""gcp-analysis-util!A1:J200"")"),"Comparison Sector")</f>
         <v>Comparison Sector</v>
       </c>
       <c r="B1" s="9" t="str">
